--- a/docs/settlements_data_dictionary_MDG.xlsx
+++ b/docs/settlements_data_dictionary_MDG.xlsx
@@ -1564,8 +1564,10 @@
       <c r="A30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>64</v>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar PV Output (kWh/year per installed kW)</t>
+        </is>
       </c>
       <c r="C30" s="2" t="s">
         <v>65</v>
